--- a/programma/2026/wk-2026-speelschema.xlsx
+++ b/programma/2026/wk-2026-speelschema.xlsx
@@ -3639,12 +3639,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>16F1</t>
+          <t>32F1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>16F1</t>
+          <t>32F1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3683,12 +3683,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>16F2</t>
+          <t>32F2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>16F2</t>
+          <t>32F2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3727,12 +3727,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>16F3</t>
+          <t>32F3</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>16F3</t>
+          <t>32F3</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>16F4</t>
+          <t>32F4</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>16F4</t>
+          <t>32F4</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3815,12 +3815,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>16F5</t>
+          <t>32F5</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>16F5</t>
+          <t>32F5</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3859,12 +3859,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>16F6</t>
+          <t>32F6</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>16F6</t>
+          <t>32F6</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3903,12 +3903,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>16F7</t>
+          <t>32F7</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>16F7</t>
+          <t>32F7</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3947,12 +3947,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>16F8</t>
+          <t>32F8</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>16F8</t>
+          <t>32F8</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3991,12 +3991,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>16F9</t>
+          <t>32F9</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>16F9</t>
+          <t>32F9</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4035,12 +4035,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>16F10</t>
+          <t>32F10</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>16F10</t>
+          <t>32F10</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4079,12 +4079,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>16F11</t>
+          <t>32F11</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>16F11</t>
+          <t>32F11</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4123,12 +4123,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>16F12</t>
+          <t>32F12</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>16F12</t>
+          <t>32F12</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4167,12 +4167,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>16F13</t>
+          <t>32F13</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>16F13</t>
+          <t>32F13</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4211,12 +4211,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>16F14</t>
+          <t>32F14</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>16F14</t>
+          <t>32F14</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4255,12 +4255,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>16F15</t>
+          <t>32F15</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>16F15</t>
+          <t>32F15</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4299,12 +4299,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>16F16</t>
+          <t>32F16</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>16F16</t>
+          <t>32F16</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4343,12 +4343,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>QF1</t>
+          <t>16F1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>QF1</t>
+          <t>16F1</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4387,12 +4387,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>QF2</t>
+          <t>16F2</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>QF2</t>
+          <t>16F2</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4431,12 +4431,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>QF3</t>
+          <t>16F3</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>QF3</t>
+          <t>16F3</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4475,12 +4475,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>QF4</t>
+          <t>16F4</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>QF4</t>
+          <t>16F4</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4519,12 +4519,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>QF5</t>
+          <t>16F5</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>QF5</t>
+          <t>16F5</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4563,12 +4563,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>QF6</t>
+          <t>16F6</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>QF6</t>
+          <t>16F6</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4607,12 +4607,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>QF7</t>
+          <t>16F7</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>QF7</t>
+          <t>16F7</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4651,12 +4651,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>QF8</t>
+          <t>16F8</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>QF8</t>
+          <t>16F8</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4695,12 +4695,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SF1</t>
+          <t>QF1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SF1</t>
+          <t>QF1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4739,12 +4739,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SF2</t>
+          <t>QF2</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SF2</t>
+          <t>QF2</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4783,12 +4783,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SF3</t>
+          <t>QF3</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SF3</t>
+          <t>QF3</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4827,12 +4827,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SF4</t>
+          <t>QF4</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SF4</t>
+          <t>QF4</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4871,12 +4871,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3RD</t>
+          <t>SF1</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>3RD</t>
+          <t>SF1</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4915,12 +4915,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3RD</t>
+          <t>SF2</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>3RD</t>
+          <t>SF2</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4959,12 +4959,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FINAL</t>
+          <t>3RD</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FINAL</t>
+          <t>3RD</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">

--- a/programma/2026/wk-2026-speelschema.xlsx
+++ b/programma/2026/wk-2026-speelschema.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13-06-2026</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Verenigde Staten</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14-06-2026</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14-06-2026</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14-06-2026</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13-06-2026</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15-06-2026</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14-06-2026</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14-06-2026</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15-06-2026</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15-06-2026</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15-06-2026</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17-06-2026</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17-06-2026</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>17-06-2026</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>17-06-2026</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>17-06-2026</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Congo</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Colombië</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>19-06-2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>19-06-2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20-06-2026</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>20-06-2026</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>20-06-2026</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>19-06-2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Verenigde Staten</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>20-06-2026</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>20-06-2026</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Colombië</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Congo</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Verenigde Staten</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>28-06-2026</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>28-06-2026</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>28-06-2026</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Colombië</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>28-06-2026</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Congo</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>28-06-2026</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>04-07-2026</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>04-07-2026</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>04-07-2026</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4368,12 +4368,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>W32F2</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>W32F5</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>04-07-2026</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>W32F1</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>W32F3</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>05-07-2026</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4456,12 +4456,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>W32F4</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>W32F6</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>W32F7</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>W32F8</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>W32F11</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>W32F12</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>07-07-2026</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4588,12 +4588,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>W32F9</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>W32F10</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>07-07-2026</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>W32F14</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>W32F16</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>07-07-2026</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>W32F13</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>W32F15</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
@@ -4705,7 +4705,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>09-07-2026</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>W16F1</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>W16F2</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>10-07-2026</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>W16F5</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>W16F6</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>11-07-2026</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>W16F3</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>W16F4</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>12-07-2026</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>W16F7</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>W16F8</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>14-07-2026</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>WQF1</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>WQF2</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>15-07-2026</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>WQF3</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>WQF4</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>18-07-2026</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>LSF1</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>LSF2</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>19-07-2026</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5028,12 +5028,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>WSF1</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nog niet bekend</t>
+          <t>WSF2</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
